--- a/xx01zvns2b/cycle_01/phafomse/Zika-NS2B-NS3-cat-c2-Pha-fo-MSE_refinement.xlsx
+++ b/xx01zvns2b/cycle_01/phafomse/Zika-NS2B-NS3-cat-c2-Pha-fo-MSE_refinement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tfb64483/Data/openbind-hippo/xx01zvns2b/cycle_01/phafomse/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DCC7364-DA8A-AC4F-A022-28126B45CD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBFDF0F-44F8-434A-8995-2D17D5C3C3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20780" yWindow="5900" windowWidth="20340" windowHeight="16940" xr2:uid="{43C74F72-DE82-444E-825C-74B22EA32B2A}"/>
+    <workbookView xWindow="13720" yWindow="880" windowWidth="27400" windowHeight="25700" xr2:uid="{43C74F72-DE82-444E-825C-74B22EA32B2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="44">
   <si>
     <t>O=C(Nc1ccc2c(c1)OCC2)c1cccc2cc[nH]c12</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>OB-00006940-001-002</t>
+  </si>
+  <si>
+    <t>smiles</t>
+  </si>
+  <si>
+    <t>compound_code</t>
+  </si>
+  <si>
+    <t>refinement_status</t>
   </si>
 </sst>
 </file>
@@ -530,26 +539,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB238DD-301A-2D4C-B3BC-FA78841B21F5}">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -557,10 +566,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -568,10 +577,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
@@ -579,10 +588,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
@@ -590,32 +599,32 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
@@ -623,21 +632,21 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -656,46 +665,46 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -711,10 +720,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -799,10 +808,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -838,29 +847,29 @@
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -920,21 +929,21 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
         <v>2</v>
@@ -942,13 +951,13 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -986,10 +995,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
         <v>16</v>
@@ -997,21 +1006,21 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
@@ -1019,10 +1028,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
@@ -1030,35 +1039,35 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1074,35 +1083,35 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1113,26 +1122,26 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
         <v>2</v>
@@ -1140,10 +1149,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
         <v>2</v>
@@ -1151,10 +1160,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
@@ -1162,10 +1171,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
         <v>2</v>
@@ -1173,21 +1182,21 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
         <v>16</v>
@@ -1195,21 +1204,21 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B61" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
         <v>2</v>
@@ -1217,54 +1226,54 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -1272,10 +1281,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C68" t="s">
         <v>2</v>
@@ -1283,13 +1292,13 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1305,21 +1314,21 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C72" t="s">
         <v>2</v>
@@ -1327,10 +1336,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
         <v>2</v>
@@ -1338,32 +1347,32 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B75" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C75" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
@@ -1371,10 +1380,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
@@ -1382,32 +1391,32 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
@@ -1415,57 +1424,57 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -1476,7 +1485,7 @@
         <v>25</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -1487,26 +1496,26 @@
         <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
@@ -1514,32 +1523,32 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
@@ -1547,13 +1556,13 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -1580,10 +1589,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
@@ -1602,10 +1611,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
         <v>16</v>
@@ -1635,10 +1644,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -1690,10 +1699,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C106" t="s">
         <v>16</v>
@@ -1767,10 +1776,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C113" t="s">
         <v>16</v>
@@ -1817,6 +1826,17 @@
         <v>40</v>
       </c>
       <c r="C117" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>39</v>
+      </c>
+      <c r="B118" t="s">
+        <v>40</v>
+      </c>
+      <c r="C118" t="s">
         <v>16</v>
       </c>
     </row>
